--- a/diseases/d127/2010-2014.xlsx
+++ b/diseases/d127/2010-2014.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -3085,9 +3082,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -5257,9 +5251,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -7429,9 +7420,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -9601,9 +9589,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -9997,9 +9982,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -10541,9 +10523,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -11085,9 +11064,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -11629,9 +11605,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -12173,9 +12146,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -12717,9 +12687,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -13261,9 +13228,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -13805,9 +13769,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -14349,9 +14310,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -14893,9 +14851,6 @@
       <c r="O88" t="n">
         <v>1</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.01946511802187685</v>
       </c>
@@ -15437,9 +15392,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -15979,9 +15931,6 @@
         <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
